--- a/data/source/weekly/cs-en-us-105pct.xlsx
+++ b/data/source/weekly/cs-en-us-105pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -895,14 +895,14 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>0</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
@@ -923,13 +923,13 @@
         <v>-50</v>
       </c>
       <c r="L15" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M15" s="15">
         <v>-50</v>
       </c>
       <c r="N15" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -939,38 +939,38 @@
       <c r="C16" s="14">
         <v>1</v>
       </c>
-      <c r="D16" s="14">
-        <v>2</v>
-      </c>
-      <c r="E16" s="15">
-        <v>-50</v>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
         <v>3</v>
       </c>
       <c r="G16" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H16" s="15">
-        <v>-57.142857142857</v>
+        <v>-40</v>
       </c>
       <c r="I16" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J16" s="14">
         <v>11</v>
       </c>
       <c r="K16" s="15">
-        <v>-63.636363636363</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="L16" s="15">
-        <v>-50</v>
+        <v>-37.5</v>
       </c>
       <c r="M16" s="15">
-        <v>-86.666666666666</v>
+        <v>-87.179487179487</v>
       </c>
       <c r="N16" s="15">
-        <v>-96.521739130434</v>
+        <v>-96.268656716417</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" s="14">
         <v>2</v>
       </c>
       <c r="E17" s="15">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="F17" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G17" s="14">
         <v>14</v>
       </c>
       <c r="H17" s="15">
-        <v>28.571428571428</v>
+        <v>50</v>
       </c>
       <c r="I17" s="14">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J17" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K17" s="15">
-        <v>-12</v>
+        <v>3.703703703703</v>
       </c>
       <c r="L17" s="15">
-        <v>-40.540540540540</v>
+        <v>-39.130434782608</v>
       </c>
       <c r="M17" s="15">
-        <v>-18.518518518518</v>
+        <v>-15.151515151515</v>
       </c>
       <c r="N17" s="15">
-        <v>-37.142857142857</v>
+        <v>-36.363636363636</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1021,38 +1021,38 @@
       <c r="C18" s="14">
         <v>1</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="D18" s="14">
+        <v>1</v>
+      </c>
+      <c r="E18" s="15">
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18" s="14">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H18" s="15">
-        <v>-80</v>
+        <v>-75</v>
       </c>
       <c r="I18" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J18" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K18" s="15">
-        <v>-60</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L18" s="15">
-        <v>-46.666666666666</v>
+        <v>-43.75</v>
       </c>
       <c r="M18" s="15">
-        <v>-80.487804878048</v>
+        <v>-82.352941176470</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.326241134751</v>
+        <v>-94.303797468354</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="F19" s="14">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G19" s="14">
         <v>31</v>
       </c>
       <c r="H19" s="15">
-        <v>0</v>
+        <v>-19.354838709677</v>
       </c>
       <c r="I19" s="14">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="J19" s="14">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="K19" s="15">
-        <v>9.302325581395</v>
+        <v>18.367346938775</v>
       </c>
       <c r="L19" s="15">
-        <v>6.818181818181</v>
+        <v>18.367346938775</v>
       </c>
       <c r="M19" s="15">
-        <v>6.818181818181</v>
+        <v>16</v>
       </c>
       <c r="N19" s="15">
-        <v>-17.543859649122</v>
+        <v>-7.936507936507</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>166.666666666667</v>
+        <v>-75</v>
       </c>
       <c r="F20" s="14">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G20" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H20" s="15">
-        <v>110</v>
+        <v>23.076923076923</v>
       </c>
       <c r="I20" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J20" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K20" s="15">
-        <v>47.058823529411</v>
+        <v>23.809523809523</v>
       </c>
       <c r="L20" s="15">
-        <v>0</v>
+        <v>-16.129032258064</v>
       </c>
       <c r="M20" s="15">
-        <v>-47.916666666666</v>
+        <v>-50</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.977528089887</v>
+        <v>-93.719806763285</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D21" s="17">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E21" s="18">
-        <v>25</v>
+        <v>38.461538461538</v>
       </c>
       <c r="F21" s="17">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="G21" s="17">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H21" s="18">
-        <v>-2.531645569620</v>
+        <v>-6.849315068493</v>
       </c>
       <c r="I21" s="17">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="J21" s="17">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="K21" s="18">
-        <v>-10.084033613445</v>
+        <v>-3.787878787878</v>
       </c>
       <c r="L21" s="18">
-        <v>-18.320610687022</v>
+        <v>-16.993464052287</v>
       </c>
       <c r="M21" s="18">
-        <v>-44.270833333333</v>
+        <v>-44.052863436123</v>
       </c>
       <c r="N21" s="18">
-        <v>-84.887005649717</v>
+        <v>-84.493284493284</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D24" s="14">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E24" s="15">
-        <v>-33.333333333333</v>
+        <v>-40</v>
       </c>
       <c r="F24" s="14">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="G24" s="14">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="H24" s="15">
-        <v>2.083333333333</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="I24" s="14">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J24" s="14">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="K24" s="15">
-        <v>18.181818181818</v>
+        <v>3.488372093023</v>
       </c>
       <c r="L24" s="15">
-        <v>-8.235294117647</v>
+        <v>-11.881188118811</v>
       </c>
       <c r="M24" s="15">
-        <v>-9.302325581395</v>
+        <v>-11</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E25" s="15">
-        <v>100</v>
+        <v>-40</v>
       </c>
       <c r="F25" s="14">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G25" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H25" s="15">
-        <v>145.454545454545</v>
+        <v>35.714285714285</v>
       </c>
       <c r="I25" s="14">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J25" s="14">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K25" s="15">
-        <v>126.666666666667</v>
+        <v>85</v>
       </c>
       <c r="L25" s="15">
-        <v>36</v>
+        <v>32.142857142857</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E26" s="15">
-        <v>-14.285714285714</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G26" s="14">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H26" s="15">
-        <v>-19.354838709677</v>
+        <v>-21.621621621621</v>
       </c>
       <c r="I26" s="14">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="J26" s="14">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="K26" s="15">
-        <v>-29.787234042553</v>
+        <v>-32.203389830508</v>
       </c>
       <c r="L26" s="15">
-        <v>17.857142857142</v>
+        <v>2.564102564102</v>
       </c>
       <c r="M26" s="15">
-        <v>-47.619047619047</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1390,32 +1390,32 @@
       <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>0</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" s="14">
         <v>2</v>
       </c>
       <c r="K27" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>-75</v>
+        <v>-60</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,35 +1428,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
         <v>5</v>
       </c>
       <c r="G28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>400</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I28" s="14">
         <v>7</v>
       </c>
       <c r="J28" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K28" s="15">
+        <v>-12.5</v>
+      </c>
+      <c r="L28" s="15">
         <v>16.666666666666</v>
-      </c>
-      <c r="L28" s="15">
-        <v>40</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1499,8 +1499,8 @@
       <c r="L29" s="15">
         <v>-100</v>
       </c>
-      <c r="M29" s="13" t="s">
-        <v>21</v>
+      <c r="M29" s="15">
+        <v>-100</v>
       </c>
       <c r="N29" s="15">
         <v>-100</v>
@@ -1540,8 +1540,8 @@
       <c r="L30" s="15">
         <v>-100</v>
       </c>
-      <c r="M30" s="13" t="s">
-        <v>21</v>
+      <c r="M30" s="15">
+        <v>-100</v>
       </c>
       <c r="N30" s="15">
         <v>-100</v>
@@ -1561,22 +1561,22 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G31" s="14">
         <v>1</v>
       </c>
       <c r="H31" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I31" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J31" s="14">
         <v>1</v>
       </c>
       <c r="K31" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-105pct.xlsx
+++ b/data/source/weekly/cs-en-us-105pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -866,11 +866,11 @@
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
@@ -884,8 +884,8 @@
       <c r="L14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M14" s="13" t="s">
-        <v>21</v>
+      <c r="M14" s="15">
+        <v>-100</v>
       </c>
       <c r="N14" s="15">
         <v>-100</v>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -905,45 +905,45 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15" s="14">
         <v>2</v>
       </c>
       <c r="K15" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="L15" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M15" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="N15" s="15">
-        <v>-75</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>1</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="14">
+        <v>2</v>
+      </c>
+      <c r="E16" s="15">
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
         <v>3</v>
@@ -958,19 +958,19 @@
         <v>5</v>
       </c>
       <c r="J16" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K16" s="15">
-        <v>-54.545454545454</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="L16" s="15">
-        <v>-37.5</v>
+        <v>-50</v>
       </c>
       <c r="M16" s="15">
-        <v>-87.179487179487</v>
+        <v>-89.130434782608</v>
       </c>
       <c r="N16" s="15">
-        <v>-96.268656716417</v>
+        <v>-96.774193548387</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>6</v>
-      </c>
-      <c r="D17" s="14">
-        <v>2</v>
-      </c>
-      <c r="E17" s="15">
+        <v>12</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" s="14">
+        <v>30</v>
+      </c>
+      <c r="G17" s="14">
+        <v>10</v>
+      </c>
+      <c r="H17" s="15">
         <v>200</v>
       </c>
-      <c r="F17" s="14">
-        <v>21</v>
-      </c>
-      <c r="G17" s="14">
-        <v>14</v>
-      </c>
-      <c r="H17" s="15">
-        <v>50</v>
-      </c>
       <c r="I17" s="14">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="J17" s="14">
         <v>27</v>
       </c>
       <c r="K17" s="15">
-        <v>3.703703703703</v>
+        <v>48.148148148148</v>
       </c>
       <c r="L17" s="15">
-        <v>-39.130434782608</v>
+        <v>-21.568627450980</v>
       </c>
       <c r="M17" s="15">
-        <v>-15.151515151515</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="N17" s="15">
-        <v>-36.363636363636</v>
+        <v>-16.666666666666</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
         <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F18" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G18" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>-75</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I18" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J18" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K18" s="15">
-        <v>-57.142857142857</v>
+        <v>-50</v>
       </c>
       <c r="L18" s="15">
-        <v>-43.75</v>
+        <v>-31.25</v>
       </c>
       <c r="M18" s="15">
-        <v>-82.352941176470</v>
+        <v>-80.701754385964</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.303797468354</v>
+        <v>-94.117647058823</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E19" s="15">
-        <v>50</v>
+        <v>-12.5</v>
       </c>
       <c r="F19" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G19" s="14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H19" s="15">
-        <v>-19.354838709677</v>
+        <v>-18.75</v>
       </c>
       <c r="I19" s="14">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="J19" s="14">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K19" s="15">
-        <v>18.367346938775</v>
+        <v>17.543859649122</v>
       </c>
       <c r="L19" s="15">
-        <v>18.367346938775</v>
+        <v>24.074074074074</v>
       </c>
       <c r="M19" s="15">
-        <v>16</v>
+        <v>13.559322033898</v>
       </c>
       <c r="N19" s="15">
-        <v>-7.936507936507</v>
+        <v>-8.219178082191</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>3</v>
+      </c>
+      <c r="D20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="14">
-        <v>4</v>
-      </c>
       <c r="E20" s="15">
-        <v>-75</v>
+        <v>200</v>
       </c>
       <c r="F20" s="14">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G20" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H20" s="15">
-        <v>23.076923076923</v>
+        <v>44.444444444444</v>
       </c>
       <c r="I20" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J20" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K20" s="15">
-        <v>23.809523809523</v>
+        <v>31.818181818181</v>
       </c>
       <c r="L20" s="15">
-        <v>-16.129032258064</v>
+        <v>-9.375</v>
       </c>
       <c r="M20" s="15">
-        <v>-50</v>
+        <v>-47.272727272727</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.719806763285</v>
+        <v>-93.776824034334</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D21" s="17">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E21" s="18">
-        <v>38.461538461538</v>
+        <v>108.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="G21" s="17">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="H21" s="18">
-        <v>-6.849315068493</v>
+        <v>21.875</v>
       </c>
       <c r="I21" s="17">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="J21" s="17">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.787878787878</v>
+        <v>6.944444444444</v>
       </c>
       <c r="L21" s="18">
-        <v>-16.993464052287</v>
+        <v>-7.228915662650</v>
       </c>
       <c r="M21" s="18">
-        <v>-44.052863436123</v>
+        <v>-42.537313432835</v>
       </c>
       <c r="N21" s="18">
-        <v>-84.493284493284</v>
+        <v>-83.547008547008</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D24" s="14">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E24" s="15">
-        <v>-40</v>
+        <v>125</v>
       </c>
       <c r="F24" s="14">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G24" s="14">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="H24" s="15">
-        <v>-26.315789473684</v>
+        <v>-3.921568627450</v>
       </c>
       <c r="I24" s="14">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="J24" s="14">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="K24" s="15">
-        <v>3.488372093023</v>
+        <v>12.765957446808</v>
       </c>
       <c r="L24" s="15">
-        <v>-11.881188118811</v>
+        <v>-6.194690265486</v>
       </c>
       <c r="M24" s="15">
-        <v>-11</v>
+        <v>-3.636363636363</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D25" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E25" s="15">
-        <v>-40</v>
+        <v>450</v>
       </c>
       <c r="F25" s="14">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G25" s="14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H25" s="15">
-        <v>35.714285714285</v>
+        <v>136.363636363636</v>
       </c>
       <c r="I25" s="14">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="J25" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K25" s="15">
-        <v>85</v>
+        <v>118.181818181818</v>
       </c>
       <c r="L25" s="15">
-        <v>32.142857142857</v>
+        <v>60</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D26" s="14">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E26" s="15">
-        <v>-41.666666666666</v>
+        <v>60</v>
       </c>
       <c r="F26" s="14">
+        <v>32</v>
+      </c>
+      <c r="G26" s="14">
         <v>29</v>
       </c>
-      <c r="G26" s="14">
-        <v>37</v>
-      </c>
       <c r="H26" s="15">
-        <v>-21.621621621621</v>
+        <v>10.344827586206</v>
       </c>
       <c r="I26" s="14">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="J26" s="14">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="K26" s="15">
-        <v>-32.203389830508</v>
+        <v>-25</v>
       </c>
       <c r="L26" s="15">
-        <v>2.564102564102</v>
+        <v>0</v>
       </c>
       <c r="M26" s="15">
         <v>-46.666666666666</v>
@@ -1397,25 +1397,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J27" s="14">
         <v>2</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L27" s="15">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1431,20 +1431,20 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G28" s="14">
         <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>66.666666666666</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I28" s="14">
         <v>7</v>
@@ -1456,7 +1456,7 @@
         <v>-12.5</v>
       </c>
       <c r="L28" s="15">
-        <v>16.666666666666</v>
+        <v>-12.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1561,13 +1561,13 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G31" s="14">
         <v>1</v>
       </c>
       <c r="H31" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I31" s="14">
         <v>3</v>

--- a/data/source/weekly/cs-en-us-105pct.xlsx
+++ b/data/source/weekly/cs-en-us-105pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -698,7 +698,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -895,32 +895,32 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
         <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
         <v>2</v>
       </c>
       <c r="J15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L15" s="15">
         <v>-33.333333333333</v>
@@ -936,82 +936,82 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>1</v>
       </c>
       <c r="D16" s="14">
         <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H16" s="15">
-        <v>-40</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J16" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K16" s="15">
-        <v>-61.538461538461</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="L16" s="15">
-        <v>-50</v>
+        <v>-30</v>
       </c>
       <c r="M16" s="15">
-        <v>-89.130434782608</v>
+        <v>-86.792452830188</v>
       </c>
       <c r="N16" s="15">
-        <v>-96.774193548387</v>
+        <v>-95.977011494252</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="14">
+      <c r="C17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="14">
+        <v>8</v>
+      </c>
+      <c r="E17" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F17" s="14">
+        <v>21</v>
+      </c>
+      <c r="G17" s="14">
         <v>12</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F17" s="14">
-        <v>30</v>
-      </c>
-      <c r="G17" s="14">
-        <v>10</v>
-      </c>
       <c r="H17" s="15">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="I17" s="14">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J17" s="14">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="K17" s="15">
-        <v>48.148148148148</v>
+        <v>8.571428571428</v>
       </c>
       <c r="L17" s="15">
-        <v>-21.568627450980</v>
+        <v>-36.666666666666</v>
       </c>
       <c r="M17" s="15">
-        <v>-11.111111111111</v>
+        <v>-20.833333333333</v>
       </c>
       <c r="N17" s="15">
-        <v>-16.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H18" s="15">
-        <v>-42.857142857142</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J18" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K18" s="15">
-        <v>-50</v>
+        <v>-52</v>
       </c>
       <c r="L18" s="15">
-        <v>-31.25</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="M18" s="15">
-        <v>-80.701754385964</v>
+        <v>-80.327868852459</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.117647058823</v>
+        <v>-94.088669950738</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D19" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>-12.5</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F19" s="14">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G19" s="14">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H19" s="15">
-        <v>-18.75</v>
+        <v>-10.714285714285</v>
       </c>
       <c r="I19" s="14">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="J19" s="14">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="K19" s="15">
-        <v>17.543859649122</v>
+        <v>12.698412698412</v>
       </c>
       <c r="L19" s="15">
-        <v>24.074074074074</v>
+        <v>10.9375</v>
       </c>
       <c r="M19" s="15">
-        <v>13.559322033898</v>
+        <v>1.428571428571</v>
       </c>
       <c r="N19" s="15">
-        <v>-8.219178082191</v>
+        <v>-14.457831325301</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>1</v>
+      </c>
+      <c r="D20" s="14">
         <v>3</v>
       </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
       <c r="E20" s="15">
-        <v>200</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F20" s="14">
         <v>13</v>
       </c>
       <c r="G20" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H20" s="15">
-        <v>44.444444444444</v>
+        <v>18.181818181818</v>
       </c>
       <c r="I20" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J20" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K20" s="15">
-        <v>31.818181818181</v>
+        <v>20</v>
       </c>
       <c r="L20" s="15">
-        <v>-9.375</v>
+        <v>-6.25</v>
       </c>
       <c r="M20" s="15">
-        <v>-47.272727272727</v>
+        <v>-51.612903225806</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.776824034334</v>
+        <v>-94.382022471910</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="D21" s="17">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="E21" s="18">
-        <v>108.333333333333</v>
+        <v>-65.217391304347</v>
       </c>
       <c r="F21" s="17">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="G21" s="17">
         <v>64</v>
       </c>
       <c r="H21" s="18">
-        <v>21.875</v>
+        <v>9.375</v>
       </c>
       <c r="I21" s="17">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="J21" s="17">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="K21" s="18">
-        <v>6.944444444444</v>
+        <v>-4.191616766467</v>
       </c>
       <c r="L21" s="18">
-        <v>-7.228915662650</v>
+        <v>-14.893617021276</v>
       </c>
       <c r="M21" s="18">
-        <v>-42.537313432835</v>
+        <v>-46.843853820598</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.547008547008</v>
+        <v>-84.891406987724</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D24" s="14">
         <v>8</v>
       </c>
       <c r="E24" s="15">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="F24" s="14">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G24" s="14">
         <v>51</v>
       </c>
       <c r="H24" s="15">
-        <v>-3.921568627450</v>
+        <v>-1.960784313725</v>
       </c>
       <c r="I24" s="14">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="J24" s="14">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="K24" s="15">
-        <v>12.765957446808</v>
+        <v>13.725490196078</v>
       </c>
       <c r="L24" s="15">
-        <v>-6.194690265486</v>
+        <v>-8.661417322834</v>
       </c>
       <c r="M24" s="15">
-        <v>-3.636363636363</v>
+        <v>-4.132231404958</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,13 +1306,13 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D25" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="15">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="F25" s="14">
         <v>26</v>
@@ -1324,16 +1324,16 @@
         <v>136.363636363636</v>
       </c>
       <c r="I25" s="14">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="J25" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K25" s="15">
-        <v>118.181818181818</v>
+        <v>134.782608695652</v>
       </c>
       <c r="L25" s="15">
-        <v>60</v>
+        <v>68.75</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D26" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E26" s="15">
-        <v>60</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="G26" s="14">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H26" s="15">
-        <v>10.344827586206</v>
+        <v>-14.814814814814</v>
       </c>
       <c r="I26" s="14">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J26" s="14">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K26" s="15">
-        <v>-25</v>
+        <v>-25.373134328358</v>
       </c>
       <c r="L26" s="15">
-        <v>0</v>
+        <v>-10.714285714285</v>
       </c>
       <c r="M26" s="15">
-        <v>-46.666666666666</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,35 +1387,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="I27" s="14">
         <v>3</v>
       </c>
       <c r="J27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>-40</v>
+        <v>-50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1456,7 +1456,7 @@
         <v>-12.5</v>
       </c>
       <c r="L28" s="15">
-        <v>-12.5</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1560,14 +1560,14 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="14">
-        <v>2</v>
-      </c>
-      <c r="G31" s="14">
-        <v>1</v>
-      </c>
-      <c r="H31" s="15">
-        <v>100</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="14">
         <v>3</v>
@@ -1578,8 +1578,8 @@
       <c r="K31" s="15">
         <v>200</v>
       </c>
-      <c r="L31" s="13" t="s">
-        <v>21</v>
+      <c r="L31" s="15">
+        <v>200</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1622,11 +1622,11 @@
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="14">
-        <v>1</v>
-      </c>
-      <c r="H33" s="15">
-        <v>-100</v>
+      <c r="G33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-105pct.xlsx
+++ b/data/source/weekly/cs-en-us-105pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -895,64 +895,64 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="14">
+      <c r="C15" s="14">
         <v>1</v>
       </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" s="14">
         <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L15" s="15">
-        <v>-33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="M15" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="N15" s="15">
-        <v>-60</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>1</v>
-      </c>
-      <c r="D16" s="14">
-        <v>2</v>
-      </c>
-      <c r="E16" s="15">
-        <v>-50</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
+        <v>3</v>
+      </c>
+      <c r="G16" s="14">
         <v>4</v>
       </c>
-      <c r="G16" s="14">
-        <v>6</v>
-      </c>
       <c r="H16" s="15">
-        <v>-33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="I16" s="14">
         <v>7</v>
@@ -964,95 +964,95 @@
         <v>-53.333333333333</v>
       </c>
       <c r="L16" s="15">
-        <v>-30</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="M16" s="15">
-        <v>-86.792452830188</v>
+        <v>-89.230769230769</v>
       </c>
       <c r="N16" s="15">
-        <v>-95.977011494252</v>
+        <v>-96.335078534031</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>20</v>
+      <c r="C17" s="14">
+        <v>2</v>
       </c>
       <c r="D17" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F17" s="14">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G17" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H17" s="15">
-        <v>75</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I17" s="14">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J17" s="14">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K17" s="15">
-        <v>8.571428571428</v>
+        <v>2.564102564102</v>
       </c>
       <c r="L17" s="15">
-        <v>-36.666666666666</v>
+        <v>-34.426229508196</v>
       </c>
       <c r="M17" s="15">
-        <v>-20.833333333333</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="N17" s="15">
-        <v>-33.333333333333</v>
+        <v>-36.507936507936</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>1</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
         <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G18" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I18" s="14">
         <v>12</v>
       </c>
       <c r="J18" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K18" s="15">
-        <v>-52</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L18" s="15">
-        <v>-36.842105263157</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M18" s="15">
-        <v>-80.327868852459</v>
+        <v>-81.818181818181</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.088669950738</v>
+        <v>-94.805194805194</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,81 +1060,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D19" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E19" s="15">
-        <v>-16.666666666666</v>
+        <v>100</v>
       </c>
       <c r="F19" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G19" s="14">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H19" s="15">
-        <v>-10.714285714285</v>
+        <v>17.391304347826</v>
       </c>
       <c r="I19" s="14">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J19" s="14">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K19" s="15">
-        <v>12.698412698412</v>
+        <v>15.151515151515</v>
       </c>
       <c r="L19" s="15">
-        <v>10.9375</v>
+        <v>4.109589041095</v>
       </c>
       <c r="M19" s="15">
-        <v>1.428571428571</v>
+        <v>1.333333333333</v>
       </c>
       <c r="N19" s="15">
-        <v>-14.457831325301</v>
+        <v>-19.148936170212</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>1</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E20" s="15">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
+        <v>5</v>
+      </c>
+      <c r="G20" s="14">
         <v>13</v>
       </c>
-      <c r="G20" s="14">
-        <v>11</v>
-      </c>
       <c r="H20" s="15">
-        <v>18.181818181818</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="I20" s="14">
         <v>30</v>
       </c>
       <c r="J20" s="14">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K20" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L20" s="15">
-        <v>-6.25</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="M20" s="15">
-        <v>-51.612903225806</v>
+        <v>-56.521739130434</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.382022471910</v>
+        <v>-94.932432432432</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21" s="17">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E21" s="18">
-        <v>-65.217391304347</v>
+        <v>-40</v>
       </c>
       <c r="F21" s="17">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="G21" s="17">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H21" s="18">
-        <v>9.375</v>
+        <v>-6.349206349206</v>
       </c>
       <c r="I21" s="17">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="J21" s="17">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="K21" s="18">
-        <v>-4.191616766467</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="L21" s="18">
-        <v>-14.893617021276</v>
+        <v>-19.230769230769</v>
       </c>
       <c r="M21" s="18">
-        <v>-46.843853820598</v>
+        <v>-50</v>
       </c>
       <c r="N21" s="18">
-        <v>-84.891406987724</v>
+        <v>-85.750636132315</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1268,34 +1268,34 @@
         <v>10</v>
       </c>
       <c r="D24" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E24" s="15">
-        <v>25</v>
+        <v>11.111111111111</v>
       </c>
       <c r="F24" s="14">
         <v>50</v>
       </c>
       <c r="G24" s="14">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="H24" s="15">
-        <v>-1.960784313725</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I24" s="14">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="J24" s="14">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="K24" s="15">
-        <v>13.725490196078</v>
+        <v>13.513513513513</v>
       </c>
       <c r="L24" s="15">
-        <v>-8.661417322834</v>
+        <v>-10.638297872340</v>
       </c>
       <c r="M24" s="15">
-        <v>-4.132231404958</v>
+        <v>-5.970149253731</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E25" s="15">
-        <v>500</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G25" s="14">
         <v>11</v>
       </c>
       <c r="H25" s="15">
-        <v>136.363636363636</v>
+        <v>100</v>
       </c>
       <c r="I25" s="14">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J25" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K25" s="15">
-        <v>134.782608695652</v>
+        <v>115.384615384615</v>
       </c>
       <c r="L25" s="15">
-        <v>68.75</v>
+        <v>60</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D26" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>-33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="F26" s="14">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G26" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H26" s="15">
-        <v>-14.814814814814</v>
+        <v>0</v>
       </c>
       <c r="I26" s="14">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="J26" s="14">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="K26" s="15">
-        <v>-25.373134328358</v>
+        <v>-18.666666666666</v>
       </c>
       <c r="L26" s="15">
-        <v>-10.714285714285</v>
+        <v>-6.153846153846</v>
       </c>
       <c r="M26" s="15">
-        <v>-54.545454545454</v>
+        <v>-49.166666666666</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,35 +1387,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="14">
+      <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="I27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J27" s="14">
         <v>3</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>-50</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,8 +1428,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>3</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1438,25 +1438,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>-66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="I28" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J28" s="14">
         <v>8</v>
       </c>
       <c r="K28" s="15">
-        <v>-12.5</v>
+        <v>25</v>
       </c>
       <c r="L28" s="15">
-        <v>-22.222222222222</v>
+        <v>11.111111111111</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1570,16 +1570,16 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J31" s="14">
         <v>1</v>
       </c>
       <c r="K31" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L31" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-105pct.xlsx
+++ b/data/source/weekly/cs-en-us-105pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -698,7 +698,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -923,54 +923,54 @@
         <v>0</v>
       </c>
       <c r="L15" s="15">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="M15" s="15">
         <v>-25</v>
       </c>
       <c r="N15" s="15">
-        <v>-40</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="C16" s="14">
+        <v>1</v>
+      </c>
+      <c r="D16" s="14">
+        <v>4</v>
+      </c>
+      <c r="E16" s="15">
+        <v>-75</v>
       </c>
       <c r="F16" s="14">
         <v>3</v>
       </c>
       <c r="G16" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H16" s="15">
-        <v>-25</v>
+        <v>-62.5</v>
       </c>
       <c r="I16" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J16" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K16" s="15">
-        <v>-53.333333333333</v>
+        <v>-57.894736842105</v>
       </c>
       <c r="L16" s="15">
-        <v>-36.363636363636</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M16" s="15">
-        <v>-89.230769230769</v>
+        <v>-89.610389610389</v>
       </c>
       <c r="N16" s="15">
-        <v>-96.335078534031</v>
+        <v>-96.153846153846</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,81 +978,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G17" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H17" s="15">
-        <v>28.571428571428</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J17" s="14">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K17" s="15">
-        <v>2.564102564102</v>
+        <v>-2.380952380952</v>
       </c>
       <c r="L17" s="15">
-        <v>-34.426229508196</v>
+        <v>-35.9375</v>
       </c>
       <c r="M17" s="15">
-        <v>-23.076923076923</v>
+        <v>-24.074074074074</v>
       </c>
       <c r="N17" s="15">
-        <v>-36.507936507936</v>
+        <v>-40.579710144927</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="F18" s="14">
         <v>4</v>
       </c>
       <c r="G18" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H18" s="15">
-        <v>-50</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="I18" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J18" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K18" s="15">
-        <v>-57.142857142857</v>
+        <v>-59.375</v>
       </c>
       <c r="L18" s="15">
-        <v>-42.857142857142</v>
+        <v>-48</v>
       </c>
       <c r="M18" s="15">
-        <v>-81.818181818181</v>
+        <v>-82.191780821917</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.805194805194</v>
+        <v>-95.038167938931</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,81 +1060,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>100</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F19" s="14">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G19" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H19" s="15">
-        <v>17.391304347826</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="I19" s="14">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="J19" s="14">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="K19" s="15">
-        <v>15.151515151515</v>
+        <v>12</v>
       </c>
       <c r="L19" s="15">
-        <v>4.109589041095</v>
+        <v>5</v>
       </c>
       <c r="M19" s="15">
-        <v>1.333333333333</v>
+        <v>-1.176470588235</v>
       </c>
       <c r="N19" s="15">
-        <v>-19.148936170212</v>
+        <v>-15.151515151515</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>-100</v>
+        <v>400</v>
       </c>
       <c r="F20" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G20" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H20" s="15">
-        <v>-61.538461538461</v>
+        <v>-10</v>
       </c>
       <c r="I20" s="14">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J20" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K20" s="15">
-        <v>0</v>
+        <v>12.903225806451</v>
       </c>
       <c r="L20" s="15">
-        <v>-21.052631578947</v>
+        <v>-12.5</v>
       </c>
       <c r="M20" s="15">
-        <v>-56.521739130434</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.932432432432</v>
+        <v>-94.656488549618</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D21" s="17">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>-40</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F21" s="17">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G21" s="17">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H21" s="18">
-        <v>-6.349206349206</v>
+        <v>-22.535211267605</v>
       </c>
       <c r="I21" s="17">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="J21" s="17">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.692307692307</v>
+        <v>-9.359605911330</v>
       </c>
       <c r="L21" s="18">
-        <v>-19.230769230769</v>
+        <v>-18.584070796460</v>
       </c>
       <c r="M21" s="18">
-        <v>-50</v>
+        <v>-50.933333333333</v>
       </c>
       <c r="N21" s="18">
-        <v>-85.750636132315</v>
+        <v>-85.867895545314</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D24" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E24" s="15">
-        <v>11.111111111111</v>
+        <v>-37.5</v>
       </c>
       <c r="F24" s="14">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G24" s="14">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="H24" s="15">
-        <v>11.111111111111</v>
+        <v>30.303030303030</v>
       </c>
       <c r="I24" s="14">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="J24" s="14">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="K24" s="15">
-        <v>13.513513513513</v>
+        <v>10.084033613445</v>
       </c>
       <c r="L24" s="15">
-        <v>-10.638297872340</v>
+        <v>-14.935064935064</v>
       </c>
       <c r="M24" s="15">
-        <v>-5.970149253731</v>
+        <v>-11.486486486486</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1309,31 +1309,31 @@
         <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E25" s="15">
-        <v>-33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="F25" s="14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G25" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H25" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I25" s="14">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J25" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K25" s="15">
-        <v>115.384615384615</v>
+        <v>114.814814814815</v>
       </c>
       <c r="L25" s="15">
-        <v>60</v>
+        <v>56.756756756756</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E26" s="15">
+        <v>125</v>
+      </c>
+      <c r="F26" s="14">
+        <v>30</v>
+      </c>
+      <c r="G26" s="14">
+        <v>20</v>
+      </c>
+      <c r="H26" s="15">
         <v>50</v>
       </c>
-      <c r="F26" s="14">
-        <v>28</v>
-      </c>
-      <c r="G26" s="14">
-        <v>28</v>
-      </c>
-      <c r="H26" s="15">
-        <v>0</v>
-      </c>
       <c r="I26" s="14">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="J26" s="14">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K26" s="15">
-        <v>-18.666666666666</v>
+        <v>-11.392405063291</v>
       </c>
       <c r="L26" s="15">
-        <v>-6.153846153846</v>
+        <v>1.449275362318</v>
       </c>
       <c r="M26" s="15">
-        <v>-49.166666666666</v>
+        <v>-46.969696969697</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,8 +1387,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1397,13 +1397,13 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
         <v>4</v>
@@ -1415,7 +1415,7 @@
         <v>33.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,14 +1428,14 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>3</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
         <v>3</v>
@@ -1450,10 +1450,10 @@
         <v>10</v>
       </c>
       <c r="J28" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K28" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L28" s="15">
         <v>11.111111111111</v>

--- a/data/source/weekly/cs-en-us-105pct.xlsx
+++ b/data/source/weekly/cs-en-us-105pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -905,13 +905,13 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
         <v>3</v>
@@ -929,7 +929,7 @@
         <v>-25</v>
       </c>
       <c r="N15" s="15">
-        <v>-50</v>
+        <v>-62.5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -940,10 +940,10 @@
         <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
         <v>3</v>
@@ -955,22 +955,22 @@
         <v>-62.5</v>
       </c>
       <c r="I16" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J16" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K16" s="15">
-        <v>-57.894736842105</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L16" s="15">
-        <v>-33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="M16" s="15">
-        <v>-89.610389610389</v>
+        <v>-88.888888888888</v>
       </c>
       <c r="N16" s="15">
-        <v>-96.153846153846</v>
+        <v>-95.871559633027</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="F17" s="14">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G17" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H17" s="15">
-        <v>-13.333333333333</v>
+        <v>-73.684210526315</v>
       </c>
       <c r="I17" s="14">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J17" s="14">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K17" s="15">
-        <v>-2.380952380952</v>
+        <v>-6.521739130434</v>
       </c>
       <c r="L17" s="15">
-        <v>-35.9375</v>
+        <v>-35.820895522388</v>
       </c>
       <c r="M17" s="15">
-        <v>-24.074074074074</v>
+        <v>-28.333333333333</v>
       </c>
       <c r="N17" s="15">
-        <v>-40.579710144927</v>
+        <v>-41.095890410958</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>3</v>
+      </c>
+      <c r="D18" s="14">
         <v>1</v>
       </c>
-      <c r="D18" s="14">
-        <v>4</v>
-      </c>
       <c r="E18" s="15">
-        <v>-75</v>
+        <v>200</v>
       </c>
       <c r="F18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G18" s="14">
         <v>11</v>
       </c>
       <c r="H18" s="15">
-        <v>-63.636363636363</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="I18" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J18" s="14">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K18" s="15">
-        <v>-59.375</v>
+        <v>-51.515151515151</v>
       </c>
       <c r="L18" s="15">
-        <v>-48</v>
+        <v>-40.740740740740</v>
       </c>
       <c r="M18" s="15">
-        <v>-82.191780821917</v>
+        <v>-81.395348837209</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.038167938931</v>
+        <v>-94.594594594594</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E19" s="15">
-        <v>-22.222222222222</v>
+        <v>-20</v>
       </c>
       <c r="F19" s="14">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G19" s="14">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H19" s="15">
-        <v>-7.692307692307</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="I19" s="14">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="J19" s="14">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="K19" s="15">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L19" s="15">
-        <v>5</v>
+        <v>-7.368421052631</v>
       </c>
       <c r="M19" s="15">
-        <v>-1.176470588235</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="N19" s="15">
-        <v>-15.151515151515</v>
+        <v>-22.807017543859</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E20" s="15">
-        <v>400</v>
+        <v>-62.5</v>
       </c>
       <c r="F20" s="14">
         <v>9</v>
       </c>
       <c r="G20" s="14">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H20" s="15">
-        <v>-10</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="I20" s="14">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J20" s="14">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="K20" s="15">
-        <v>12.903225806451</v>
+        <v>-2.564102564102</v>
       </c>
       <c r="L20" s="15">
-        <v>-12.5</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="M20" s="15">
-        <v>-54.545454545454</v>
+        <v>-54.216867469879</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.656488549618</v>
+        <v>-94.729542302357</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D21" s="17">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>-28.571428571428</v>
+        <v>-35</v>
       </c>
       <c r="F21" s="17">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G21" s="17">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H21" s="18">
-        <v>-22.535211267605</v>
+        <v>-43.037974683544</v>
       </c>
       <c r="I21" s="17">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="J21" s="17">
-        <v>203</v>
+        <v>223</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.359605911330</v>
+        <v>-11.659192825112</v>
       </c>
       <c r="L21" s="18">
-        <v>-18.584070796460</v>
+        <v>-21.2</v>
       </c>
       <c r="M21" s="18">
-        <v>-50.933333333333</v>
+        <v>-52.068126520681</v>
       </c>
       <c r="N21" s="18">
-        <v>-85.867895545314</v>
+        <v>-86.262203626220</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D24" s="14">
         <v>8</v>
       </c>
       <c r="E24" s="15">
-        <v>-37.5</v>
+        <v>12.5</v>
       </c>
       <c r="F24" s="14">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="G24" s="14">
         <v>33</v>
       </c>
       <c r="H24" s="15">
-        <v>30.303030303030</v>
+        <v>3.030303030303</v>
       </c>
       <c r="I24" s="14">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="J24" s="14">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="K24" s="15">
-        <v>10.084033613445</v>
+        <v>10.236220472440</v>
       </c>
       <c r="L24" s="15">
-        <v>-14.935064935064</v>
+        <v>-14.110429447852</v>
       </c>
       <c r="M24" s="15">
-        <v>-11.486486486486</v>
+        <v>-15.151515151515</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
         <v>1</v>
       </c>
       <c r="E25" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F25" s="14">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G25" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H25" s="15">
-        <v>200</v>
+        <v>116.666666666667</v>
       </c>
       <c r="I25" s="14">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J25" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K25" s="15">
-        <v>114.814814814815</v>
+        <v>117.857142857143</v>
       </c>
       <c r="L25" s="15">
-        <v>56.756756756756</v>
+        <v>60.526315789473</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D26" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E26" s="15">
-        <v>125</v>
+        <v>20</v>
       </c>
       <c r="F26" s="14">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G26" s="14">
         <v>20</v>
       </c>
       <c r="H26" s="15">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I26" s="14">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="J26" s="14">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="K26" s="15">
-        <v>-11.392405063291</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="L26" s="15">
-        <v>1.449275362318</v>
+        <v>-1.298701298701</v>
       </c>
       <c r="M26" s="15">
-        <v>-46.969696969697</v>
+        <v>-47.586206896551</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1397,13 +1397,13 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
         <v>4</v>
@@ -1431,11 +1431,11 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
         <v>3</v>
@@ -1456,7 +1456,7 @@
         <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>11.111111111111</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-105pct.xlsx
+++ b/data/source/weekly/cs-en-us-105pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -907,11 +907,11 @@
       <c r="F15" s="14">
         <v>1</v>
       </c>
-      <c r="G15" s="14">
-        <v>1</v>
-      </c>
-      <c r="H15" s="15">
-        <v>0</v>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="14">
         <v>3</v>
@@ -929,48 +929,48 @@
         <v>-25</v>
       </c>
       <c r="N15" s="15">
-        <v>-62.5</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="14">
         <v>1</v>
       </c>
-      <c r="D16" s="14">
+      <c r="E16" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F16" s="14">
         <v>2</v>
       </c>
-      <c r="E16" s="15">
-        <v>-50</v>
-      </c>
-      <c r="F16" s="14">
-        <v>3</v>
-      </c>
       <c r="G16" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H16" s="15">
-        <v>-62.5</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="I16" s="14">
         <v>9</v>
       </c>
       <c r="J16" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K16" s="15">
-        <v>-57.142857142857</v>
+        <v>-59.090909090909</v>
       </c>
       <c r="L16" s="15">
-        <v>-25</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="M16" s="15">
-        <v>-88.888888888888</v>
+        <v>-89.285714285714</v>
       </c>
       <c r="N16" s="15">
-        <v>-95.871559633027</v>
+        <v>-96.153846153846</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>-50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G17" s="14">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H17" s="15">
-        <v>-73.684210526315</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="I17" s="14">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J17" s="14">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K17" s="15">
-        <v>-6.521739130434</v>
+        <v>-4.081632653061</v>
       </c>
       <c r="L17" s="15">
-        <v>-35.820895522388</v>
+        <v>-34.722222222222</v>
       </c>
       <c r="M17" s="15">
-        <v>-28.333333333333</v>
+        <v>-29.850746268656</v>
       </c>
       <c r="N17" s="15">
-        <v>-41.095890410958</v>
+        <v>-42.682926829268</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E18" s="15">
-        <v>200</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H18" s="15">
-        <v>-54.545454545454</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I18" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J18" s="14">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="K18" s="15">
-        <v>-51.515151515151</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="L18" s="15">
-        <v>-40.740740740740</v>
+        <v>-40</v>
       </c>
       <c r="M18" s="15">
-        <v>-81.395348837209</v>
+        <v>-80.434782608695</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.594594594594</v>
+        <v>-94.690265486725</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>-20</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F19" s="14">
         <v>22</v>
       </c>
       <c r="G19" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H19" s="15">
-        <v>-4.347826086956</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="I19" s="14">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="J19" s="14">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K19" s="15">
-        <v>10</v>
+        <v>4.494382022471</v>
       </c>
       <c r="L19" s="15">
-        <v>-7.368421052631</v>
+        <v>-7</v>
       </c>
       <c r="M19" s="15">
-        <v>-4.347826086956</v>
+        <v>-9.708737864077</v>
       </c>
       <c r="N19" s="15">
-        <v>-22.807017543859</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E20" s="15">
-        <v>-62.5</v>
+        <v>-80</v>
       </c>
       <c r="F20" s="14">
         <v>9</v>
       </c>
       <c r="G20" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H20" s="15">
-        <v>-47.058823529411</v>
+        <v>-52.631578947368</v>
       </c>
       <c r="I20" s="14">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J20" s="14">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="K20" s="15">
-        <v>-2.564102564102</v>
+        <v>-11.363636363636</v>
       </c>
       <c r="L20" s="15">
-        <v>-13.636363636363</v>
+        <v>-18.75</v>
       </c>
       <c r="M20" s="15">
-        <v>-54.216867469879</v>
+        <v>-57.608695652173</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.729542302357</v>
+        <v>-95.161290322580</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E21" s="18">
-        <v>-35</v>
+        <v>-50</v>
       </c>
       <c r="F21" s="17">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G21" s="17">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H21" s="18">
-        <v>-43.037974683544</v>
+        <v>-38.75</v>
       </c>
       <c r="I21" s="17">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="J21" s="17">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="K21" s="18">
-        <v>-11.659192825112</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="L21" s="18">
-        <v>-21.2</v>
+        <v>-22.014925373134</v>
       </c>
       <c r="M21" s="18">
-        <v>-52.068126520681</v>
+        <v>-53.348214285714</v>
       </c>
       <c r="N21" s="18">
-        <v>-86.262203626220</v>
+        <v>-86.929330831769</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
+        <v>8</v>
+      </c>
+      <c r="D24" s="14">
         <v>9</v>
       </c>
-      <c r="D24" s="14">
-        <v>8</v>
-      </c>
       <c r="E24" s="15">
-        <v>12.5</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F24" s="14">
+        <v>32</v>
+      </c>
+      <c r="G24" s="14">
         <v>34</v>
       </c>
-      <c r="G24" s="14">
-        <v>33</v>
-      </c>
       <c r="H24" s="15">
-        <v>3.030303030303</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="I24" s="14">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="J24" s="14">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="K24" s="15">
-        <v>10.236220472440</v>
+        <v>8.823529411764</v>
       </c>
       <c r="L24" s="15">
-        <v>-14.110429447852</v>
+        <v>-14.942528735632</v>
       </c>
       <c r="M24" s="15">
-        <v>-15.151515151515</v>
+        <v>-19.125683060109</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D25" s="14">
         <v>1</v>
       </c>
       <c r="E25" s="15">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F25" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G25" s="14">
         <v>6</v>
       </c>
       <c r="H25" s="15">
-        <v>116.666666666667</v>
+        <v>100</v>
       </c>
       <c r="I25" s="14">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="J25" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K25" s="15">
-        <v>117.857142857143</v>
+        <v>127.586206896552</v>
       </c>
       <c r="L25" s="15">
-        <v>60.526315789473</v>
+        <v>57.142857142857</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E26" s="15">
-        <v>20</v>
+        <v>-50</v>
       </c>
       <c r="F26" s="14">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G26" s="14">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="H26" s="15">
-        <v>45</v>
+        <v>9.677419354838</v>
       </c>
       <c r="I26" s="14">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="J26" s="14">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="K26" s="15">
-        <v>-9.523809523809</v>
+        <v>-15.306122448979</v>
       </c>
       <c r="L26" s="15">
-        <v>-1.298701298701</v>
+        <v>2.469135802469</v>
       </c>
       <c r="M26" s="15">
-        <v>-47.586206896551</v>
+        <v>-46.103896103896</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1399,11 +1399,11 @@
       <c r="F27" s="14">
         <v>1</v>
       </c>
-      <c r="G27" s="14">
-        <v>1</v>
-      </c>
-      <c r="H27" s="15">
-        <v>0</v>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I27" s="14">
         <v>4</v>
@@ -1428,8 +1428,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>2</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1438,25 +1438,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
         <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="I28" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J28" s="14">
         <v>10</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L28" s="15">
-        <v>-9.090909090909</v>
+        <v>9.090909090909</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-105pct.xlsx
+++ b/data/source/weekly/cs-en-us-105pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -904,8 +904,8 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="14">
-        <v>1</v>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -923,54 +923,54 @@
         <v>0</v>
       </c>
       <c r="L15" s="15">
-        <v>-40</v>
+        <v>-50</v>
       </c>
       <c r="M15" s="15">
         <v>-25</v>
       </c>
       <c r="N15" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>1</v>
       </c>
       <c r="D16" s="14">
         <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H16" s="15">
-        <v>-71.428571428571</v>
+        <v>-62.5</v>
       </c>
       <c r="I16" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J16" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K16" s="15">
-        <v>-59.090909090909</v>
+        <v>-56.521739130434</v>
       </c>
       <c r="L16" s="15">
-        <v>-30.769230769230</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M16" s="15">
-        <v>-89.285714285714</v>
+        <v>-88.372093023255</v>
       </c>
       <c r="N16" s="15">
-        <v>-96.153846153846</v>
+        <v>-96.047430830039</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,81 +978,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D17" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E17" s="15">
-        <v>33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="F17" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G17" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H17" s="15">
-        <v>-35.714285714285</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="I17" s="14">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="J17" s="14">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K17" s="15">
-        <v>-4.081632653061</v>
+        <v>-7.017543859649</v>
       </c>
       <c r="L17" s="15">
-        <v>-34.722222222222</v>
+        <v>-26.388888888888</v>
       </c>
       <c r="M17" s="15">
-        <v>-29.850746268656</v>
+        <v>-27.397260273972</v>
       </c>
       <c r="N17" s="15">
-        <v>-42.682926829268</v>
+        <v>-38.372093023255</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>2</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
         <v>6</v>
       </c>
       <c r="G18" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H18" s="15">
-        <v>-57.142857142857</v>
+        <v>-62.5</v>
       </c>
       <c r="I18" s="14">
         <v>18</v>
       </c>
       <c r="J18" s="14">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="K18" s="15">
-        <v>-53.846153846153</v>
+        <v>-59.090909090909</v>
       </c>
       <c r="L18" s="15">
-        <v>-40</v>
+        <v>-48.571428571428</v>
       </c>
       <c r="M18" s="15">
-        <v>-80.434782608695</v>
+        <v>-81.818181818181</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.690265486725</v>
+        <v>-95.212765957446</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D19" s="14">
         <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>-44.444444444444</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F19" s="14">
         <v>22</v>
       </c>
       <c r="G19" s="14">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H19" s="15">
-        <v>-15.384615384615</v>
+        <v>-31.25</v>
       </c>
       <c r="I19" s="14">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="J19" s="14">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="K19" s="15">
-        <v>4.494382022471</v>
+        <v>1.020408163265</v>
       </c>
       <c r="L19" s="15">
-        <v>-7</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="M19" s="15">
-        <v>-9.708737864077</v>
+        <v>-13.913043478260</v>
       </c>
       <c r="N19" s="15">
-        <v>-25</v>
+        <v>-27.737226277372</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G20" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H20" s="15">
-        <v>-52.631578947368</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="I20" s="14">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J20" s="14">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K20" s="15">
-        <v>-11.363636363636</v>
+        <v>-10.416666666666</v>
       </c>
       <c r="L20" s="15">
-        <v>-18.75</v>
+        <v>-23.214285714285</v>
       </c>
       <c r="M20" s="15">
-        <v>-57.608695652173</v>
+        <v>-58.252427184466</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.161290322580</v>
+        <v>-95.173961840628</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E21" s="18">
-        <v>-50</v>
+        <v>-37.037037037037</v>
       </c>
       <c r="F21" s="17">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G21" s="17">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H21" s="18">
-        <v>-38.75</v>
+        <v>-38.043478260869</v>
       </c>
       <c r="I21" s="17">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="J21" s="17">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="K21" s="18">
-        <v>-15.384615384615</v>
+        <v>-17.518248175182</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.014925373134</v>
+        <v>-22.336769759450</v>
       </c>
       <c r="M21" s="18">
-        <v>-53.348214285714</v>
+        <v>-53.497942386831</v>
       </c>
       <c r="N21" s="18">
-        <v>-86.929330831769</v>
+        <v>-87.159090909090</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D24" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E24" s="15">
-        <v>-11.111111111111</v>
+        <v>50</v>
       </c>
       <c r="F24" s="14">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G24" s="14">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H24" s="15">
-        <v>-5.882352941176</v>
+        <v>0</v>
       </c>
       <c r="I24" s="14">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="J24" s="14">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="K24" s="15">
-        <v>8.823529411764</v>
+        <v>10.563380281690</v>
       </c>
       <c r="L24" s="15">
-        <v>-14.942528735632</v>
+        <v>-15.591397849462</v>
       </c>
       <c r="M24" s="15">
-        <v>-19.125683060109</v>
+        <v>-23.414634146341</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1309,31 +1309,31 @@
         <v>5</v>
       </c>
       <c r="D25" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" s="15">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="F25" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G25" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H25" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I25" s="14">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J25" s="14">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K25" s="15">
-        <v>127.586206896552</v>
+        <v>129.032258064516</v>
       </c>
       <c r="L25" s="15">
-        <v>57.142857142857</v>
+        <v>65.116279069767</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1350,34 +1350,34 @@
         <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E26" s="15">
-        <v>-50</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G26" s="14">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H26" s="15">
-        <v>9.677419354838</v>
+        <v>-17.142857142857</v>
       </c>
       <c r="I26" s="14">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="J26" s="14">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="K26" s="15">
-        <v>-15.306122448979</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="L26" s="15">
-        <v>2.469135802469</v>
+        <v>3.448275862068</v>
       </c>
       <c r="M26" s="15">
-        <v>-46.103896103896</v>
+        <v>-44.099378881987</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,8 +1387,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1406,16 +1406,16 @@
         <v>21</v>
       </c>
       <c r="I27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J27" s="14">
         <v>3</v>
       </c>
       <c r="K27" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>-50</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,23 +1428,23 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="14">
         <v>2</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="14">
-        <v>5</v>
       </c>
       <c r="G28" s="14">
         <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
         <v>12</v>
@@ -1456,7 +1456,7 @@
         <v>20</v>
       </c>
       <c r="L28" s="15">
-        <v>9.090909090909</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-105pct.xlsx
+++ b/data/source/weekly/cs-en-us-105pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>2</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -904,8 +904,8 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
+      <c r="F15" s="14">
+        <v>2</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -914,22 +914,22 @@
         <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J15" s="14">
         <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>0</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L15" s="15">
-        <v>-50</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M15" s="15">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="N15" s="15">
-        <v>-75</v>
+        <v>-58.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -940,37 +940,37 @@
         <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
         <v>3</v>
       </c>
       <c r="G16" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H16" s="15">
-        <v>-62.5</v>
+        <v>-50</v>
       </c>
       <c r="I16" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J16" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K16" s="15">
-        <v>-56.521739130434</v>
+        <v>-52</v>
       </c>
       <c r="L16" s="15">
-        <v>-28.571428571428</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M16" s="15">
-        <v>-88.372093023255</v>
+        <v>-86.363636363636</v>
       </c>
       <c r="N16" s="15">
-        <v>-96.047430830039</v>
+        <v>-95.588235294117</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,81 +978,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D17" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>-25</v>
+        <v>-80</v>
       </c>
       <c r="F17" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G17" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H17" s="15">
-        <v>-27.777777777777</v>
+        <v>-30</v>
       </c>
       <c r="I17" s="14">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J17" s="14">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="K17" s="15">
-        <v>-7.017543859649</v>
+        <v>-11.290322580645</v>
       </c>
       <c r="L17" s="15">
-        <v>-26.388888888888</v>
+        <v>-31.25</v>
       </c>
       <c r="M17" s="15">
-        <v>-27.397260273972</v>
+        <v>-27.631578947368</v>
       </c>
       <c r="N17" s="15">
-        <v>-38.372093023255</v>
+        <v>-39.560439560439</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>2</v>
       </c>
       <c r="D18" s="14">
         <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>-60</v>
       </c>
       <c r="F18" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G18" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H18" s="15">
-        <v>-62.5</v>
+        <v>-58.823529411764</v>
       </c>
       <c r="I18" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J18" s="14">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K18" s="15">
-        <v>-59.090909090909</v>
+        <v>-59.183673469387</v>
       </c>
       <c r="L18" s="15">
-        <v>-48.571428571428</v>
+        <v>-47.368421052631</v>
       </c>
       <c r="M18" s="15">
-        <v>-81.818181818181</v>
+        <v>-80.769230769230</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.212765957446</v>
+        <v>-95.180722891566</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>-33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="F19" s="14">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G19" s="14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H19" s="15">
-        <v>-31.25</v>
+        <v>-3.333333333333</v>
       </c>
       <c r="I19" s="14">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="J19" s="14">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="K19" s="15">
-        <v>1.020408163265</v>
+        <v>7.619047619047</v>
       </c>
       <c r="L19" s="15">
-        <v>-8.333333333333</v>
+        <v>-2.586206896551</v>
       </c>
       <c r="M19" s="15">
-        <v>-13.913043478260</v>
+        <v>-12.403100775193</v>
       </c>
       <c r="N19" s="15">
-        <v>-27.737226277372</v>
+        <v>-24.161073825503</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>-80</v>
       </c>
       <c r="F20" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G20" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H20" s="15">
-        <v>-27.777777777777</v>
+        <v>-59.090909090909</v>
       </c>
       <c r="I20" s="14">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J20" s="14">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K20" s="15">
-        <v>-10.416666666666</v>
+        <v>-16.981132075471</v>
       </c>
       <c r="L20" s="15">
-        <v>-23.214285714285</v>
+        <v>-25.423728813559</v>
       </c>
       <c r="M20" s="15">
-        <v>-58.252427184466</v>
+        <v>-58.878504672897</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.173961840628</v>
+        <v>-95.454545454545</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D21" s="17">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E21" s="18">
-        <v>-37.037037037037</v>
+        <v>-12.5</v>
       </c>
       <c r="F21" s="17">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G21" s="17">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H21" s="18">
-        <v>-38.043478260869</v>
+        <v>-32.631578947368</v>
       </c>
       <c r="I21" s="17">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="J21" s="17">
-        <v>274</v>
+        <v>298</v>
       </c>
       <c r="K21" s="18">
-        <v>-17.518248175182</v>
+        <v>-16.442953020134</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.336769759450</v>
+        <v>-20.447284345047</v>
       </c>
       <c r="M21" s="18">
-        <v>-53.497942386831</v>
+        <v>-51.556420233463</v>
       </c>
       <c r="N21" s="18">
-        <v>-87.159090909090</v>
+        <v>-86.976987447698</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D24" s="14">
         <v>6</v>
       </c>
       <c r="E24" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F24" s="14">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="G24" s="14">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H24" s="15">
-        <v>0</v>
+        <v>37.931034482758</v>
       </c>
       <c r="I24" s="14">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="J24" s="14">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="K24" s="15">
-        <v>10.563380281690</v>
+        <v>14.189189189189</v>
       </c>
       <c r="L24" s="15">
-        <v>-15.591397849462</v>
+        <v>-12.886597938144</v>
       </c>
       <c r="M24" s="15">
-        <v>-23.414634146341</v>
+        <v>-22.477064220183</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D25" s="14">
         <v>2</v>
       </c>
       <c r="E25" s="15">
-        <v>150</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G25" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H25" s="15">
-        <v>200</v>
+        <v>133.333333333333</v>
       </c>
       <c r="I25" s="14">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J25" s="14">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K25" s="15">
-        <v>129.032258064516</v>
+        <v>118.181818181818</v>
       </c>
       <c r="L25" s="15">
-        <v>65.116279069767</v>
+        <v>67.441860465116</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D26" s="14">
         <v>12</v>
       </c>
       <c r="E26" s="15">
-        <v>-41.666666666666</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G26" s="14">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="H26" s="15">
-        <v>-17.142857142857</v>
+        <v>-41.860465116279</v>
       </c>
       <c r="I26" s="14">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J26" s="14">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="K26" s="15">
-        <v>-18.181818181818</v>
+        <v>-22.131147540983</v>
       </c>
       <c r="L26" s="15">
-        <v>3.448275862068</v>
+        <v>3.260869565217</v>
       </c>
       <c r="M26" s="15">
-        <v>-44.099378881987</v>
+        <v>-45.714285714285</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,7 +1388,7 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1397,7 +1397,7 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1406,16 +1406,16 @@
         <v>21</v>
       </c>
       <c r="I27" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J27" s="14">
         <v>3</v>
       </c>
       <c r="K27" s="15">
-        <v>66.666666666666</v>
+        <v>133.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>-44.444444444444</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1431,32 +1431,32 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
         <v>2</v>
       </c>
       <c r="G28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I28" s="14">
         <v>12</v>
       </c>
       <c r="J28" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K28" s="15">
-        <v>20</v>
+        <v>9.090909090909</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-105pct.xlsx
+++ b/data/source/weekly/cs-en-us-105pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -896,7 +896,7 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -905,7 +905,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -914,63 +914,63 @@
         <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J15" s="14">
         <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="L15" s="15">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="M15" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N15" s="15">
-        <v>-58.333333333333</v>
+        <v>-53.846153846153</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="14">
         <v>1</v>
       </c>
-      <c r="D16" s="14">
+      <c r="E16" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F16" s="14">
         <v>2</v>
       </c>
-      <c r="E16" s="15">
-        <v>-50</v>
-      </c>
-      <c r="F16" s="14">
-        <v>3</v>
-      </c>
       <c r="G16" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H16" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="I16" s="14">
         <v>12</v>
       </c>
       <c r="J16" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K16" s="15">
-        <v>-52</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="L16" s="15">
-        <v>-14.285714285714</v>
+        <v>-20</v>
       </c>
       <c r="M16" s="15">
-        <v>-86.363636363636</v>
+        <v>-87.368421052631</v>
       </c>
       <c r="N16" s="15">
-        <v>-95.588235294117</v>
+        <v>-95.876288659793</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G17" s="14">
         <v>20</v>
       </c>
       <c r="H17" s="15">
-        <v>-30</v>
+        <v>-20</v>
       </c>
       <c r="I17" s="14">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="J17" s="14">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K17" s="15">
-        <v>-11.290322580645</v>
+        <v>-10.606060606060</v>
       </c>
       <c r="L17" s="15">
-        <v>-31.25</v>
+        <v>-28.915662650602</v>
       </c>
       <c r="M17" s="15">
-        <v>-27.631578947368</v>
+        <v>-30.588235294117</v>
       </c>
       <c r="N17" s="15">
-        <v>-39.560439560439</v>
+        <v>-37.894736842105</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1022,37 +1022,37 @@
         <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>-60</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G18" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H18" s="15">
-        <v>-58.823529411764</v>
+        <v>-68.421052631578</v>
       </c>
       <c r="I18" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J18" s="14">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K18" s="15">
-        <v>-59.183673469387</v>
+        <v>-57.692307692307</v>
       </c>
       <c r="L18" s="15">
-        <v>-47.368421052631</v>
+        <v>-43.589743589743</v>
       </c>
       <c r="M18" s="15">
-        <v>-80.769230769230</v>
+        <v>-79.439252336448</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.180722891566</v>
+        <v>-95.227765726681</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E19" s="15">
-        <v>100</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="F19" s="14">
         <v>29</v>
       </c>
       <c r="G19" s="14">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H19" s="15">
-        <v>-3.333333333333</v>
+        <v>-19.444444444444</v>
       </c>
       <c r="I19" s="14">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="J19" s="14">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="K19" s="15">
-        <v>7.619047619047</v>
+        <v>0.862068965517</v>
       </c>
       <c r="L19" s="15">
-        <v>-2.586206896551</v>
+        <v>-4.098360655737</v>
       </c>
       <c r="M19" s="15">
-        <v>-12.403100775193</v>
+        <v>-16.428571428571</v>
       </c>
       <c r="N19" s="15">
-        <v>-24.161073825503</v>
+        <v>-25.949367088607</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>2</v>
+      </c>
+      <c r="D20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="14">
-        <v>5</v>
-      </c>
       <c r="E20" s="15">
-        <v>-80</v>
+        <v>100</v>
       </c>
       <c r="F20" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G20" s="14">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H20" s="15">
-        <v>-59.090909090909</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="I20" s="14">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J20" s="14">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K20" s="15">
-        <v>-16.981132075471</v>
+        <v>-14.814814814814</v>
       </c>
       <c r="L20" s="15">
-        <v>-25.423728813559</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M20" s="15">
-        <v>-58.878504672897</v>
+        <v>-58.928571428571</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.454545454545</v>
+        <v>-95.564127290260</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,13 +1142,13 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D21" s="17">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>-12.5</v>
+        <v>-35</v>
       </c>
       <c r="F21" s="17">
         <v>64</v>
@@ -1160,22 +1160,22 @@
         <v>-32.631578947368</v>
       </c>
       <c r="I21" s="17">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="J21" s="17">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="K21" s="18">
-        <v>-16.442953020134</v>
+        <v>-17.610062893081</v>
       </c>
       <c r="L21" s="18">
-        <v>-20.447284345047</v>
+        <v>-21.556886227544</v>
       </c>
       <c r="M21" s="18">
-        <v>-51.556420233463</v>
+        <v>-52.450090744101</v>
       </c>
       <c r="N21" s="18">
-        <v>-86.976987447698</v>
+        <v>-87.287724405628</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D24" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E24" s="15">
-        <v>100</v>
+        <v>-12.5</v>
       </c>
       <c r="F24" s="14">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G24" s="14">
         <v>29</v>
       </c>
       <c r="H24" s="15">
-        <v>37.931034482758</v>
+        <v>31.034482758620</v>
       </c>
       <c r="I24" s="14">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="J24" s="14">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="K24" s="15">
-        <v>14.189189189189</v>
+        <v>12.820512820512</v>
       </c>
       <c r="L24" s="15">
-        <v>-12.886597938144</v>
+        <v>-13.725490196078</v>
       </c>
       <c r="M24" s="15">
-        <v>-22.477064220183</v>
+        <v>-24.786324786324</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1309,31 +1309,31 @@
         <v>1</v>
       </c>
       <c r="D25" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E25" s="15">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="F25" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G25" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H25" s="15">
-        <v>133.333333333333</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I25" s="14">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J25" s="14">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K25" s="15">
-        <v>118.181818181818</v>
+        <v>97.297297297297</v>
       </c>
       <c r="L25" s="15">
-        <v>67.441860465116</v>
+        <v>58.695652173913</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D26" s="14">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E26" s="15">
-        <v>-58.333333333333</v>
+        <v>28.571428571428</v>
       </c>
       <c r="F26" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G26" s="14">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H26" s="15">
-        <v>-41.860465116279</v>
+        <v>-37.777777777777</v>
       </c>
       <c r="I26" s="14">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="J26" s="14">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="K26" s="15">
-        <v>-22.131147540983</v>
+        <v>-19.379844961240</v>
       </c>
       <c r="L26" s="15">
-        <v>3.260869565217</v>
+        <v>8.333333333333</v>
       </c>
       <c r="M26" s="15">
-        <v>-45.714285714285</v>
+        <v>-44.086021505376</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,7 +1388,7 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1397,7 +1397,7 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1406,16 +1406,16 @@
         <v>21</v>
       </c>
       <c r="I27" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J27" s="14">
         <v>3</v>
       </c>
       <c r="K27" s="15">
-        <v>133.333333333333</v>
+        <v>166.666666666667</v>
       </c>
       <c r="L27" s="15">
-        <v>-22.222222222222</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1441,22 +1441,22 @@
         <v>2</v>
       </c>
       <c r="G28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
         <v>12</v>
       </c>
       <c r="J28" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K28" s="15">
-        <v>9.090909090909</v>
+        <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>-14.285714285714</v>
+        <v>-20</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1554,29 +1554,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>-100</v>
       </c>
       <c r="I31" s="14">
         <v>2</v>
       </c>
       <c r="J31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L31" s="15">
         <v>100</v>

--- a/data/source/weekly/cs-en-us-105pct.xlsx
+++ b/data/source/weekly/cs-en-us-105pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -896,7 +896,7 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -905,7 +905,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -914,63 +914,63 @@
         <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J15" s="14">
         <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L15" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M15" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N15" s="15">
-        <v>-53.846153846153</v>
+        <v>-35.714285714285</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H16" s="15">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="I16" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J16" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K16" s="15">
-        <v>-53.846153846153</v>
+        <v>-53.571428571428</v>
       </c>
       <c r="L16" s="15">
-        <v>-20</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="M16" s="15">
-        <v>-87.368421052631</v>
+        <v>-87</v>
       </c>
       <c r="N16" s="15">
-        <v>-95.876288659793</v>
+        <v>-95.911949685534</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -981,37 +981,37 @@
         <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G17" s="14">
         <v>20</v>
       </c>
       <c r="H17" s="15">
-        <v>-20</v>
+        <v>-10</v>
       </c>
       <c r="I17" s="14">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="J17" s="14">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K17" s="15">
-        <v>-10.606060606060</v>
+        <v>-5.797101449275</v>
       </c>
       <c r="L17" s="15">
-        <v>-28.915662650602</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M17" s="15">
-        <v>-30.588235294117</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="N17" s="15">
-        <v>-37.894736842105</v>
+        <v>-35</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
-      </c>
-      <c r="D18" s="14">
-        <v>3</v>
-      </c>
-      <c r="E18" s="15">
-        <v>-33.333333333333</v>
+        <v>1</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H18" s="15">
-        <v>-68.421052631578</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="I18" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J18" s="14">
         <v>52</v>
       </c>
       <c r="K18" s="15">
-        <v>-57.692307692307</v>
+        <v>-55.769230769230</v>
       </c>
       <c r="L18" s="15">
-        <v>-43.589743589743</v>
+        <v>-43.902439024390</v>
       </c>
       <c r="M18" s="15">
-        <v>-79.439252336448</v>
+        <v>-79.646017699115</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.227765726681</v>
+        <v>-95.445544554455</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E19" s="15">
-        <v>-63.636363636363</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G19" s="14">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H19" s="15">
-        <v>-19.444444444444</v>
+        <v>-17.948717948717</v>
       </c>
       <c r="I19" s="14">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="J19" s="14">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="K19" s="15">
-        <v>0.862068965517</v>
+        <v>-1.5625</v>
       </c>
       <c r="L19" s="15">
-        <v>-4.098360655737</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="M19" s="15">
-        <v>-16.428571428571</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="N19" s="15">
-        <v>-25.949367088607</v>
+        <v>-24.550898203592</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>100</v>
+        <v>-75</v>
       </c>
       <c r="F20" s="14">
         <v>8</v>
       </c>
       <c r="G20" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H20" s="15">
-        <v>-46.666666666666</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I20" s="14">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J20" s="14">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="K20" s="15">
-        <v>-14.814814814814</v>
+        <v>-18.965517241379</v>
       </c>
       <c r="L20" s="15">
-        <v>-33.333333333333</v>
+        <v>-37.333333333333</v>
       </c>
       <c r="M20" s="15">
-        <v>-58.928571428571</v>
+        <v>-60.169491525423</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.564127290260</v>
+        <v>-95.692025664528</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>-35</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F21" s="17">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="G21" s="17">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H21" s="18">
-        <v>-32.631578947368</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="I21" s="17">
-        <v>262</v>
+        <v>283</v>
       </c>
       <c r="J21" s="17">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="K21" s="18">
-        <v>-17.610062893081</v>
+        <v>-16.519174041297</v>
       </c>
       <c r="L21" s="18">
-        <v>-21.556886227544</v>
+        <v>-21.606648199446</v>
       </c>
       <c r="M21" s="18">
-        <v>-52.450090744101</v>
+        <v>-51.290877796901</v>
       </c>
       <c r="N21" s="18">
-        <v>-87.287724405628</v>
+        <v>-87.142208087233</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D24" s="14">
         <v>8</v>
       </c>
       <c r="E24" s="15">
-        <v>-12.5</v>
+        <v>112.5</v>
       </c>
       <c r="F24" s="14">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="G24" s="14">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H24" s="15">
-        <v>31.034482758620</v>
+        <v>67.857142857142</v>
       </c>
       <c r="I24" s="14">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="J24" s="14">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="K24" s="15">
-        <v>12.820512820512</v>
+        <v>17.682926829268</v>
       </c>
       <c r="L24" s="15">
-        <v>-13.725490196078</v>
+        <v>-11.059907834101</v>
       </c>
       <c r="M24" s="15">
-        <v>-24.786324786324</v>
+        <v>-24.313725490196</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D25" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E25" s="15">
-        <v>-75</v>
+        <v>150</v>
       </c>
       <c r="F25" s="14">
         <v>12</v>
       </c>
       <c r="G25" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H25" s="15">
-        <v>33.333333333333</v>
+        <v>20</v>
       </c>
       <c r="I25" s="14">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="J25" s="14">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K25" s="15">
-        <v>97.297297297297</v>
+        <v>100</v>
       </c>
       <c r="L25" s="15">
-        <v>58.695652173913</v>
+        <v>59.183673469387</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D26" s="14">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E26" s="15">
-        <v>28.571428571428</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G26" s="14">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H26" s="15">
-        <v>-37.777777777777</v>
+        <v>-25.581395348837</v>
       </c>
       <c r="I26" s="14">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="J26" s="14">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="K26" s="15">
-        <v>-19.379844961240</v>
+        <v>-18.439716312056</v>
       </c>
       <c r="L26" s="15">
-        <v>8.333333333333</v>
+        <v>11.650485436893</v>
       </c>
       <c r="M26" s="15">
-        <v>-44.086021505376</v>
+        <v>-41.919191919191</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,7 +1388,7 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1397,7 +1397,7 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1406,16 +1406,16 @@
         <v>21</v>
       </c>
       <c r="I27" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J27" s="14">
         <v>3</v>
       </c>
       <c r="K27" s="15">
-        <v>166.666666666667</v>
+        <v>266.666666666667</v>
       </c>
       <c r="L27" s="15">
-        <v>-11.111111111111</v>
+        <v>22.222222222222</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,14 +1428,14 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-100</v>
+      <c r="C28" s="14">
+        <v>2</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
         <v>2</v>
@@ -1447,16 +1447,16 @@
         <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J28" s="14">
         <v>12</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L28" s="15">
-        <v>-20</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1564,7 +1564,7 @@
         <v>20</v>
       </c>
       <c r="G31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="15">
         <v>-100</v>
@@ -1573,10 +1573,10 @@
         <v>2</v>
       </c>
       <c r="J31" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K31" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L31" s="15">
         <v>100</v>

--- a/data/source/weekly/cs-en-us-105pct.xlsx
+++ b/data/source/weekly/cs-en-us-105pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -896,7 +896,7 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -926,10 +926,10 @@
         <v>50</v>
       </c>
       <c r="M15" s="15">
-        <v>50</v>
+        <v>28.571428571428</v>
       </c>
       <c r="N15" s="15">
-        <v>-35.714285714285</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
         <v>-50</v>
       </c>
       <c r="F16" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H16" s="15">
-        <v>-50</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="I16" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J16" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K16" s="15">
-        <v>-53.571428571428</v>
+        <v>-53.125</v>
       </c>
       <c r="L16" s="15">
-        <v>-13.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M16" s="15">
-        <v>-87</v>
+        <v>-85.576923076923</v>
       </c>
       <c r="N16" s="15">
-        <v>-95.911949685534</v>
+        <v>-95.454545454545</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D17" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E17" s="15">
-        <v>33.333333333333</v>
+        <v>600</v>
       </c>
       <c r="F17" s="14">
         <v>18</v>
       </c>
       <c r="G17" s="14">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H17" s="15">
-        <v>-10</v>
+        <v>38.461538461538</v>
       </c>
       <c r="I17" s="14">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="J17" s="14">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K17" s="15">
-        <v>-5.797101449275</v>
+        <v>4.285714285714</v>
       </c>
       <c r="L17" s="15">
-        <v>-28.571428571428</v>
+        <v>-23.157894736842</v>
       </c>
       <c r="M17" s="15">
-        <v>-28.571428571428</v>
+        <v>-24.742268041237</v>
       </c>
       <c r="N17" s="15">
-        <v>-35</v>
+        <v>-30.476190476190</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1021,38 +1021,38 @@
       <c r="C18" s="14">
         <v>1</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="D18" s="14">
+        <v>4</v>
+      </c>
+      <c r="E18" s="15">
+        <v>-75</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H18" s="15">
-        <v>-61.538461538461</v>
+        <v>-50</v>
       </c>
       <c r="I18" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J18" s="14">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K18" s="15">
-        <v>-55.769230769230</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L18" s="15">
-        <v>-43.902439024390</v>
+        <v>-44.186046511627</v>
       </c>
       <c r="M18" s="15">
-        <v>-79.646017699115</v>
+        <v>-80</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.445544554455</v>
+        <v>-95.604395604395</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>9</v>
+      </c>
+      <c r="D19" s="14">
         <v>8</v>
       </c>
-      <c r="D19" s="14">
-        <v>12</v>
-      </c>
       <c r="E19" s="15">
-        <v>-33.333333333333</v>
+        <v>12.5</v>
       </c>
       <c r="F19" s="14">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G19" s="14">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H19" s="15">
-        <v>-17.948717948717</v>
+        <v>-7.894736842105</v>
       </c>
       <c r="I19" s="14">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="J19" s="14">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="K19" s="15">
-        <v>-1.5625</v>
+        <v>-0.735294117647</v>
       </c>
       <c r="L19" s="15">
-        <v>-5.263157894736</v>
+        <v>-2.173913043478</v>
       </c>
       <c r="M19" s="15">
-        <v>-14.285714285714</v>
+        <v>-12.903225806451</v>
       </c>
       <c r="N19" s="15">
-        <v>-24.550898203592</v>
+        <v>-24.581005586592</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G20" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H20" s="15">
-        <v>-42.857142857142</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="I20" s="14">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J20" s="14">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K20" s="15">
-        <v>-18.965517241379</v>
+        <v>-18.032786885245</v>
       </c>
       <c r="L20" s="15">
-        <v>-37.333333333333</v>
+        <v>-35.897435897435</v>
       </c>
       <c r="M20" s="15">
-        <v>-60.169491525423</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.692025664528</v>
+        <v>-95.640802092415</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D21" s="17">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>-14.285714285714</v>
+        <v>15</v>
       </c>
       <c r="F21" s="17">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G21" s="17">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="H21" s="18">
-        <v>-21.739130434782</v>
+        <v>-10.588235294117</v>
       </c>
       <c r="I21" s="17">
-        <v>283</v>
+        <v>306</v>
       </c>
       <c r="J21" s="17">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="K21" s="18">
-        <v>-16.519174041297</v>
+        <v>-14.763231197771</v>
       </c>
       <c r="L21" s="18">
-        <v>-21.606648199446</v>
+        <v>-18.4</v>
       </c>
       <c r="M21" s="18">
-        <v>-51.290877796901</v>
+        <v>-49.753694581280</v>
       </c>
       <c r="N21" s="18">
-        <v>-87.142208087233</v>
+        <v>-86.855670103092</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D24" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E24" s="15">
-        <v>112.5</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G24" s="14">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H24" s="15">
-        <v>67.857142857142</v>
+        <v>29.411764705882</v>
       </c>
       <c r="I24" s="14">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="J24" s="14">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="K24" s="15">
-        <v>17.682926829268</v>
+        <v>14.204545454545</v>
       </c>
       <c r="L24" s="15">
-        <v>-11.059907834101</v>
+        <v>-14.102564102564</v>
       </c>
       <c r="M24" s="15">
-        <v>-24.313725490196</v>
+        <v>-23.574144486692</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
         <v>2</v>
       </c>
       <c r="E25" s="15">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F25" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G25" s="14">
         <v>10</v>
       </c>
       <c r="H25" s="15">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I25" s="14">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J25" s="14">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K25" s="15">
         <v>100</v>
       </c>
       <c r="L25" s="15">
-        <v>59.183673469387</v>
+        <v>64</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1350,34 +1350,34 @@
         <v>12</v>
       </c>
       <c r="D26" s="14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F26" s="14">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G26" s="14">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="H26" s="15">
-        <v>-25.581395348837</v>
+        <v>-2.564102564102</v>
       </c>
       <c r="I26" s="14">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="J26" s="14">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="K26" s="15">
-        <v>-18.439716312056</v>
+        <v>-14.765100671140</v>
       </c>
       <c r="L26" s="15">
-        <v>11.650485436893</v>
+        <v>8.547008547008</v>
       </c>
       <c r="M26" s="15">
-        <v>-41.919191919191</v>
+        <v>-38.048780487804</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,7 +1388,7 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1397,7 +1397,7 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1429,34 +1429,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="E28" s="15">
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G28" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
         <v>0</v>
       </c>
       <c r="I28" s="14">
+        <v>16</v>
+      </c>
+      <c r="J28" s="14">
         <v>14</v>
       </c>
-      <c r="J28" s="14">
-        <v>12</v>
-      </c>
       <c r="K28" s="15">
-        <v>16.666666666666</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L28" s="15">
-        <v>-6.666666666666</v>
+        <v>6.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1554,11 +1554,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-105pct.xlsx
+++ b/data/source/weekly/cs-en-us-105pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -895,32 +895,32 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>6</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+        <v>4</v>
+      </c>
+      <c r="G15" s="14">
+        <v>1</v>
+      </c>
+      <c r="H15" s="15">
+        <v>300</v>
       </c>
       <c r="I15" s="14">
         <v>9</v>
       </c>
       <c r="J15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="L15" s="15">
         <v>50</v>
@@ -940,37 +940,37 @@
         <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G16" s="14">
         <v>9</v>
       </c>
       <c r="H16" s="15">
-        <v>-55.555555555555</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="I16" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J16" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K16" s="15">
-        <v>-53.125</v>
+        <v>-50</v>
       </c>
       <c r="L16" s="15">
-        <v>0</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="M16" s="15">
-        <v>-85.576923076923</v>
+        <v>-84.259259259259</v>
       </c>
       <c r="N16" s="15">
-        <v>-95.454545454545</v>
+        <v>-95.100864553314</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -981,78 +981,78 @@
         <v>7</v>
       </c>
       <c r="D17" s="14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>600</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G17" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H17" s="15">
-        <v>38.461538461538</v>
+        <v>71.428571428571</v>
       </c>
       <c r="I17" s="14">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="J17" s="14">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="K17" s="15">
-        <v>4.285714285714</v>
+        <v>5.263157894736</v>
       </c>
       <c r="L17" s="15">
-        <v>-23.157894736842</v>
+        <v>-20</v>
       </c>
       <c r="M17" s="15">
-        <v>-24.742268041237</v>
+        <v>-20</v>
       </c>
       <c r="N17" s="15">
-        <v>-30.476190476190</v>
+        <v>-29.824561403508</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>1</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
+        <v>2</v>
+      </c>
+      <c r="E18" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F18" s="14">
         <v>4</v>
       </c>
-      <c r="E18" s="15">
-        <v>-75</v>
-      </c>
-      <c r="F18" s="14">
-        <v>6</v>
-      </c>
       <c r="G18" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H18" s="15">
-        <v>-50</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="I18" s="14">
         <v>24</v>
       </c>
       <c r="J18" s="14">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K18" s="15">
-        <v>-57.142857142857</v>
+        <v>-58.620689655172</v>
       </c>
       <c r="L18" s="15">
-        <v>-44.186046511627</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="M18" s="15">
-        <v>-80</v>
+        <v>-80.952380952380</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.604395604395</v>
+        <v>-95.854922279792</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D19" s="14">
         <v>8</v>
       </c>
       <c r="E19" s="15">
-        <v>12.5</v>
+        <v>-62.5</v>
       </c>
       <c r="F19" s="14">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="G19" s="14">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H19" s="15">
-        <v>-7.894736842105</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="I19" s="14">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="J19" s="14">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="K19" s="15">
-        <v>-0.735294117647</v>
+        <v>-4.166666666666</v>
       </c>
       <c r="L19" s="15">
-        <v>-2.173913043478</v>
+        <v>-4.166666666666</v>
       </c>
       <c r="M19" s="15">
-        <v>-12.903225806451</v>
+        <v>-15.337423312883</v>
       </c>
       <c r="N19" s="15">
-        <v>-24.581005586592</v>
+        <v>-28.497409326424</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1103,38 +1103,38 @@
       <c r="C20" s="14">
         <v>3</v>
       </c>
-      <c r="D20" s="14">
-        <v>3</v>
-      </c>
-      <c r="E20" s="15">
-        <v>0</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G20" s="14">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H20" s="15">
-        <v>-46.153846153846</v>
+        <v>12.5</v>
       </c>
       <c r="I20" s="14">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J20" s="14">
         <v>61</v>
       </c>
       <c r="K20" s="15">
-        <v>-18.032786885245</v>
+        <v>-13.114754098360</v>
       </c>
       <c r="L20" s="15">
-        <v>-35.897435897435</v>
+        <v>-33.75</v>
       </c>
       <c r="M20" s="15">
-        <v>-58.333333333333</v>
+        <v>-59.230769230769</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.640802092415</v>
+        <v>-95.598006644518</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E21" s="18">
-        <v>15</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="F21" s="17">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G21" s="17">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H21" s="18">
-        <v>-10.588235294117</v>
+        <v>-12.5</v>
       </c>
       <c r="I21" s="17">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="J21" s="17">
-        <v>359</v>
+        <v>378</v>
       </c>
       <c r="K21" s="18">
-        <v>-14.763231197771</v>
+        <v>-15.079365079365</v>
       </c>
       <c r="L21" s="18">
-        <v>-18.4</v>
+        <v>-18.320610687022</v>
       </c>
       <c r="M21" s="18">
-        <v>-49.753694581280</v>
+        <v>-49.84375</v>
       </c>
       <c r="N21" s="18">
-        <v>-86.855670103092</v>
+        <v>-86.940602115541</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D24" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E24" s="15">
-        <v>-33.333333333333</v>
+        <v>-18.75</v>
       </c>
       <c r="F24" s="14">
+        <v>45</v>
+      </c>
+      <c r="G24" s="14">
         <v>44</v>
       </c>
-      <c r="G24" s="14">
-        <v>34</v>
-      </c>
       <c r="H24" s="15">
-        <v>29.411764705882</v>
+        <v>2.272727272727</v>
       </c>
       <c r="I24" s="14">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="J24" s="14">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="K24" s="15">
-        <v>14.204545454545</v>
+        <v>11.458333333333</v>
       </c>
       <c r="L24" s="15">
-        <v>-14.102564102564</v>
+        <v>-13.360323886639</v>
       </c>
       <c r="M24" s="15">
-        <v>-23.574144486692</v>
+        <v>-29.372937293729</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E25" s="15">
-        <v>100</v>
+        <v>-40</v>
       </c>
       <c r="F25" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G25" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H25" s="15">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I25" s="14">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J25" s="14">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="K25" s="15">
-        <v>100</v>
+        <v>84.782608695652</v>
       </c>
       <c r="L25" s="15">
-        <v>64</v>
+        <v>54.545454545454</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E26" s="15">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="F26" s="14">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="G26" s="14">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H26" s="15">
-        <v>-2.564102564102</v>
+        <v>46.875</v>
       </c>
       <c r="I26" s="14">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="J26" s="14">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="K26" s="15">
-        <v>-14.765100671140</v>
+        <v>-8.441558441558</v>
       </c>
       <c r="L26" s="15">
-        <v>8.547008547008</v>
+        <v>15.573770491803</v>
       </c>
       <c r="M26" s="15">
-        <v>-38.048780487804</v>
+        <v>-36.771300448430</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1390,32 +1390,32 @@
       <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>6</v>
-      </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+        <v>5</v>
+      </c>
+      <c r="G27" s="14">
+        <v>1</v>
+      </c>
+      <c r="H27" s="15">
+        <v>400</v>
       </c>
       <c r="I27" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K27" s="15">
-        <v>266.666666666667</v>
+        <v>200</v>
       </c>
       <c r="L27" s="15">
-        <v>22.222222222222</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,14 +1428,14 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
       <c r="E28" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
         <v>4</v>
@@ -1450,13 +1450,13 @@
         <v>16</v>
       </c>
       <c r="J28" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K28" s="15">
-        <v>14.285714285714</v>
+        <v>6.666666666666</v>
       </c>
       <c r="L28" s="15">
-        <v>6.666666666666</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1579,7 +1579,7 @@
         <v>-33.333333333333</v>
       </c>
       <c r="L31" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
